--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="998">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -2994,6 +2994,18 @@
   </si>
   <si>
     <t>RUA JORGE COELHO, 147</t>
+  </si>
+  <si>
+    <t>2513 - KAENA PARTICIPAÇÕES LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2346854600017</t>
+  </si>
+  <si>
+    <t>01455070</t>
+  </si>
+  <si>
+    <t>RUA ANGELINA MAFFEI VITA, 314 - AP 81</t>
   </si>
 </sst>
 </file>
@@ -3280,7 +3292,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E326"/>
+  <dimension ref="A1:E327"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="74.5714285714286" customWidth="1" style="1"/>
@@ -8823,6 +8835,23 @@
         <v>140</v>
       </c>
     </row>
+    <row ht="12.75" customHeight="1" r="327">
+      <c r="A327" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="E327" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>
   <pageSetup orientation="portrait" pageOrder="downThenOver" paperSize="9" fitToWidth="0" fitToHeight="0"/>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="1005">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -2996,16 +2996,37 @@
     <t>RUA JORGE COELHO, 147</t>
   </si>
   <si>
-    <t>2513 - KAENA PARTICIPAÇÕES LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2346854600017</t>
+    <t>2513 - KAENA PARTICIPAÇÕES LTDA - II</t>
   </si>
   <si>
     <t>01455070</t>
   </si>
   <si>
     <t>RUA ANGELINA MAFFEI VITA, 314 - AP 81</t>
+  </si>
+  <si>
+    <t>231601 - MARCO FREIRE (ÁREA EXTERNA)</t>
+  </si>
+  <si>
+    <t>AVENIDA LÚCIO COSTA, 4260, APTO 602/BL03</t>
+  </si>
+  <si>
+    <t>2515 - MARCO FREIRE (ÁREA EXTERNA)</t>
+  </si>
+  <si>
+    <t>051.359.547-32</t>
+  </si>
+  <si>
+    <t>AVENIDA LÚCIO COSTA 4260, APTO 602/BL03</t>
+  </si>
+  <si>
+    <t>2514 - FELIPE HESS BORGES (SANTA BRANCA)</t>
+  </si>
+  <si>
+    <t>12380000</t>
+  </si>
+  <si>
+    <t>ESTR. PART. FRANCISCO DE ASSIS, 1224</t>
   </si>
 </sst>
 </file>
@@ -3292,7 +3313,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E327"/>
+  <dimension ref="A1:E330"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="74.5714285714286" customWidth="1" style="1"/>
@@ -8840,15 +8861,66 @@
         <v>994</v>
       </c>
       <c r="B327" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="C327" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="C327" s="1" t="s">
+      <c r="D327" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="D327" s="1" t="s">
+      <c r="E327" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="328">
+      <c r="A328" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="E327" s="1" t="s">
+      <c r="B328" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="E328" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="329">
+      <c r="A329" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E329" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="330">
+      <c r="A330" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E330" s="1" t="s">
         <v>140</v>
       </c>
     </row>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -2900,7 +2900,7 @@
     <t>RUA SERIDÓ, 106 - APART. 211D</t>
   </si>
   <si>
-    <t>2504 - MARIA ANGÉLICA A. MONTEIRO DA COSTA</t>
+    <t>2504 - MARIA ANGÉLICA A. M. DA COSTA</t>
   </si>
   <si>
     <t>73451100797</t>
@@ -3020,7 +3020,7 @@
     <t>AVENIDA LÚCIO COSTA 4260, APTO 602/BL03</t>
   </si>
   <si>
-    <t>2514 - FELIPE HESS BORGES (SANTA BRANCA)</t>
+    <t>2514 - FELIPE HESS BORGES</t>
   </si>
   <si>
     <t>12380000</t>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="365">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -1062,6 +1062,18 @@
   </si>
   <si>
     <t xml:space="preserve"> 04351672862</t>
+  </si>
+  <si>
+    <t>2601 - REGINA CAMPOS SALLES MORAES ABREU</t>
+  </si>
+  <si>
+    <t>04383430856</t>
+  </si>
+  <si>
+    <t>01456010</t>
+  </si>
+  <si>
+    <t>RUA CAMPO VERDE, 262 - CASA 04</t>
   </si>
   <si>
     <t>9991 - DÉBITO ADMINISTRAÇÃO (OBRAS)</t>
@@ -1381,7 +1393,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
@@ -3140,7 +3152,7 @@
         <v>353</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="104">
@@ -3148,13 +3160,13 @@
         <v>354</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>14</v>
@@ -3162,52 +3174,69 @@
     </row>
     <row ht="12.75" customHeight="1" r="105">
       <c r="A105" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>357</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="106">
       <c r="A106" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>249</v>
+        <v>360</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>250</v>
+        <v>79</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="107">
       <c r="A107" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="108">
+      <c r="A108" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D108" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E108" s="1" t="s">
         <v>14</v>
       </c>
     </row>

--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="388">
   <si>
     <t>EMPREENDIMENTO</t>
   </si>
@@ -1076,6 +1076,57 @@
     <t>RUA CAMPO VERDE, 262 - CASA 04</t>
   </si>
   <si>
+    <t>2602 - RENATA STUHLBERGER</t>
+  </si>
+  <si>
+    <t>22761084870</t>
+  </si>
+  <si>
+    <t>01423010</t>
+  </si>
+  <si>
+    <t>RUA BATATAES 586, APT 91</t>
+  </si>
+  <si>
+    <t>2603 - FERNANDO AUGUSTO COELHO F DE VASCONCELLOS</t>
+  </si>
+  <si>
+    <t>22420041</t>
+  </si>
+  <si>
+    <t>RUA PRUDENTE DE MORAIS, 1117</t>
+  </si>
+  <si>
+    <t>2604 - ANDRE FRANCO SALES</t>
+  </si>
+  <si>
+    <t>27799045850</t>
+  </si>
+  <si>
+    <t>RD SUMARÉ MONTE MOR KM09 - HARAS LARISSA</t>
+  </si>
+  <si>
+    <t>2605 - ALESSANDRO ARDUINI</t>
+  </si>
+  <si>
+    <t>33034896883</t>
+  </si>
+  <si>
+    <t>04538083</t>
+  </si>
+  <si>
+    <t>AVENIDA HORÁCIO LAFER, 815 - 8º ANDAR</t>
+  </si>
+  <si>
+    <t>2606 - MARCO FREIRE (FAZENDA BOA VISTA)</t>
+  </si>
+  <si>
+    <t>18540000</t>
+  </si>
+  <si>
+    <t>FAZENDA BOA VISTA, QUADRA VII, LOTE 11</t>
+  </si>
+  <si>
     <t>9991 - DÉBITO ADMINISTRAÇÃO (OBRAS)</t>
   </si>
   <si>
@@ -1100,6 +1151,15 @@
     <t>RUA PINTASSILGO</t>
   </si>
   <si>
+    <t>230801 - CRISTINA FRAGA</t>
+  </si>
+  <si>
+    <t>158.928.017-21</t>
+  </si>
+  <si>
+    <t>RUA PEDROSO ALVARENGA</t>
+  </si>
+  <si>
     <t>231601 - MARCO FREIRE (ÁREA EXTERNA)</t>
   </si>
   <si>
@@ -1107,6 +1167,15 @@
   </si>
   <si>
     <t>240401 - LUIZ HENRIQUE FRAGA (PÓS-OBRA)</t>
+  </si>
+  <si>
+    <t>251001 - LUIZ ANTONIO BETTIOL</t>
+  </si>
+  <si>
+    <t>27981940168</t>
+  </si>
+  <si>
+    <t>AVENIDA VIEIRA SOUTO, 250</t>
   </si>
 </sst>
 </file>
@@ -1393,7 +1462,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="57.7142857142857" customWidth="1" style="1"/>
@@ -3169,7 +3238,7 @@
         <v>357</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="105">
@@ -3177,13 +3246,13 @@
         <v>358</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>355</v>
+        <v>294</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>14</v>
@@ -3191,16 +3260,16 @@
     </row>
     <row ht="12.75" customHeight="1" r="106">
       <c r="A106" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>9</v>
@@ -3208,35 +3277,154 @@
     </row>
     <row ht="12.75" customHeight="1" r="107">
       <c r="A107" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>249</v>
+        <v>365</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>250</v>
+        <v>366</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="108">
       <c r="A108" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="109">
+      <c r="A109" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="110">
+      <c r="A110" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="111">
+      <c r="A111" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="112">
+      <c r="A112" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="113">
+      <c r="A113" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="114">
+      <c r="A114" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D114" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E114" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="115">
+      <c r="A115" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>14</v>
       </c>
     </row>
